--- a/rmonize/data_schema/Dataschema_P2.xlsx
+++ b/rmonize/data_schema/Dataschema_P2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\rmonize\data_schema\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\rmonize\data_schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA70F85-3D3F-4243-8F92-69513F4710CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007AC5BF-B6C4-4BD2-A3C0-86BAE84EA577}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14895" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="261">
   <si>
     <t>index</t>
   </si>
@@ -670,24 +670,6 @@
     <t>female</t>
   </si>
   <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>primary school completed</t>
-  </si>
-  <si>
-    <t>technical/professional school completed</t>
-  </si>
-  <si>
-    <t>secondary school</t>
-  </si>
-  <si>
-    <t>longer education (incl. university)</t>
-  </si>
-  <si>
-    <t>not specified</t>
-  </si>
-  <si>
     <t>employed-full time</t>
   </si>
   <si>
@@ -800,6 +782,36 @@
   </si>
   <si>
     <t>Sodium intake [mg/d]</t>
+  </si>
+  <si>
+    <t>Early Childhood Education</t>
+  </si>
+  <si>
+    <t>Primary Education</t>
+  </si>
+  <si>
+    <t>Lower Secondary Education</t>
+  </si>
+  <si>
+    <t>Upper Secondary Education</t>
+  </si>
+  <si>
+    <t>Post-secondary non-tertiary education</t>
+  </si>
+  <si>
+    <t>Short-Cycle Tertiary Education</t>
+  </si>
+  <si>
+    <t>Bachelor's or equivalent level</t>
+  </si>
+  <si>
+    <t>Master's or equivalent level</t>
+  </si>
+  <si>
+    <t>Doctoral or equivalent level</t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
 </sst>
 </file>
@@ -853,9 +865,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -871,9 +883,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -911,7 +923,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1017,7 +1029,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1159,7 +1171,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1168,7 +1180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D109"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625"/>
     <col min="2" max="2" width="34.140625" bestFit="1" customWidth="1"/>
@@ -1744,7 +1756,7 @@
         <v>84</v>
       </c>
       <c r="C41" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -1772,7 +1784,7 @@
         <v>87</v>
       </c>
       <c r="C43" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -1800,7 +1812,7 @@
         <v>90</v>
       </c>
       <c r="C45" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
@@ -1828,7 +1840,7 @@
         <v>93</v>
       </c>
       <c r="C47" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
@@ -1856,7 +1868,7 @@
         <v>96</v>
       </c>
       <c r="C49" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
@@ -1884,7 +1896,7 @@
         <v>99</v>
       </c>
       <c r="C51" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -1912,7 +1924,7 @@
         <v>102</v>
       </c>
       <c r="C53" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -1940,7 +1952,7 @@
         <v>105</v>
       </c>
       <c r="C55" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -1968,7 +1980,7 @@
         <v>108</v>
       </c>
       <c r="C57" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -2010,7 +2022,7 @@
         <v>114</v>
       </c>
       <c r="C60" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
@@ -2038,7 +2050,7 @@
         <v>117</v>
       </c>
       <c r="C62" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
@@ -2500,7 +2512,7 @@
         <v>182</v>
       </c>
       <c r="C95" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D95" t="s">
         <v>11</v>
@@ -2514,7 +2526,7 @@
         <v>183</v>
       </c>
       <c r="C96" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D96" t="s">
         <v>11</v>
@@ -2717,8 +2729,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C98"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C102"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="53.140625" bestFit="1" customWidth="1"/>
@@ -2762,7 +2774,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2773,7 +2785,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2784,7 +2796,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -2795,7 +2807,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -2806,7 +2818,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2817,7 +2829,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -2825,46 +2837,46 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>219</v>
+        <v>257</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2872,10 +2884,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2883,10 +2895,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -2894,147 +2906,147 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
         <v>226</v>
@@ -3045,7 +3057,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
         <v>227</v>
@@ -3056,32 +3068,32 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -3089,10 +3101,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -3100,10 +3112,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -3111,10 +3123,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -3122,10 +3134,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B37" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -3133,10 +3145,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -3144,10 +3156,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B39" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -3155,10 +3167,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -3166,131 +3178,131 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B41" t="s">
-        <v>254</v>
+        <v>220</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B43" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B44" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B45" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B49" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B51" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -3298,10 +3310,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B53" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -3309,10 +3321,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -3320,10 +3332,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B55" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -3331,10 +3343,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -3342,10 +3354,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B57" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -3353,10 +3365,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -3364,10 +3376,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B59" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -3375,10 +3387,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B60" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -3386,10 +3398,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B61" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -3397,10 +3409,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B62" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -3408,10 +3420,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B63" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -3419,10 +3431,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B64" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -3430,10 +3442,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B65" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -3441,10 +3453,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B66" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3452,10 +3464,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B67" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -3463,10 +3475,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B68" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -3474,10 +3486,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B69" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -3485,10 +3497,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B70" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -3496,10 +3508,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B71" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -3507,10 +3519,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -3518,10 +3530,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B73" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -3529,10 +3541,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -3540,21 +3552,21 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C75">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B76" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3562,10 +3574,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -3573,10 +3585,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B78" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3584,21 +3596,21 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B79" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C79">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B80" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -3606,10 +3618,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B81" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -3617,10 +3629,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B82" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -3628,10 +3640,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B83" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -3639,10 +3651,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B84" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -3650,10 +3662,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B85" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -3661,10 +3673,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B86" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -3672,10 +3684,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B87" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -3683,10 +3695,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B88" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -3694,10 +3706,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B89" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -3705,10 +3717,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B90" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -3716,10 +3728,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B91" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -3727,10 +3739,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="B92" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -3738,10 +3750,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="B93" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -3749,24 +3761,24 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>208</v>
+        <v>120</v>
       </c>
       <c r="B94" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>208</v>
+        <v>120</v>
       </c>
       <c r="B95" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="C95">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3774,10 +3786,10 @@
         <v>208</v>
       </c>
       <c r="B96" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C96">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3785,10 +3797,10 @@
         <v>208</v>
       </c>
       <c r="B97" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3796,9 +3808,53 @@
         <v>208</v>
       </c>
       <c r="B98" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>208</v>
+      </c>
+      <c r="B99" t="s">
+        <v>233</v>
+      </c>
+      <c r="C99">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>208</v>
+      </c>
+      <c r="B100" t="s">
+        <v>234</v>
+      </c>
+      <c r="C100">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>208</v>
+      </c>
+      <c r="B101" t="s">
+        <v>235</v>
+      </c>
+      <c r="C101">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>208</v>
+      </c>
+      <c r="B102" t="s">
+        <v>236</v>
+      </c>
+      <c r="C102">
         <v>6</v>
       </c>
     </row>
@@ -3811,36 +3867,36 @@
     </customSheetView>
   </customSheetViews>
   <hyperlinks>
-    <hyperlink ref="A20" r:id="rId2" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:SMOKE_ST:Dataschema" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="A30" r:id="rId3" display="https://www.maelstrom-research.org/variable/canpath-f1-hrfq-hp:F1_WH_HRT_EVER:Dataschema" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="A71" r:id="rId4" display="https://www.maelstrom-research.org/variable/canpath-f1-hrfq-hp:F1_DIS_MI_AGE:Dataschema" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="A34" r:id="rId5" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_HYP:Dataschema" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="A36" r:id="rId6" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_CVD:Dataschema" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="A63" r:id="rId7" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:MED_STAT:Dataschema" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="A65" r:id="rId8" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:MED_NSAID:Dataschema" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="A32" r:id="rId9" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_DIAB:Dataschema" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="A38" r:id="rId10" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_CVD:Dataschema" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="A14" r:id="rId11" display="https://www.maelstrom-research.org/variable/chpt-qual-hp:WRK_EMPLOYMENT:Dataschema" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="A24" r:id="rId12" display="https://www.maelstrom-research.org/variable/helti-c-12m-hp:MED_SUPP_VITD_C_12M:Dataschema" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="A83" r:id="rId13" display="https://www.maelstrom-research.org/variable/canpath-f1-hrfq-hp:F1_DIS_DIAB_TYPE2:Dataschema" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="A11" r:id="rId14" display="https://www.maelstrom-research.org/variable/chpt-qual-hp:WRK_EMPLOYMENT:Dataschema" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="A10" r:id="rId15" display="https://www.maelstrom-research.org/variable/chpt-qual-hp:WRK_EMPLOYMENT:Dataschema" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="A15" r:id="rId16" display="https://www.maelstrom-research.org/variable/chpt-qual-hp:WRK_EMPLOYMENT:Dataschema" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
-    <hyperlink ref="A16" r:id="rId17" display="https://www.maelstrom-research.org/variable/chpt-qual-hp:WRK_EMPLOYMENT:Dataschema" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
-    <hyperlink ref="A13" r:id="rId18" display="https://www.maelstrom-research.org/variable/chpt-qual-hp:WRK_EMPLOYMENT:Dataschema" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
-    <hyperlink ref="A12" r:id="rId19" display="https://www.maelstrom-research.org/variable/chpt-qual-hp:WRK_EMPLOYMENT:Dataschema" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
-    <hyperlink ref="A19" r:id="rId20" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:SMOKE_ST:Dataschema" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
-    <hyperlink ref="A21" r:id="rId21" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:SMOKE_ST:Dataschema" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
-    <hyperlink ref="A23" r:id="rId22" display="https://www.maelstrom-research.org/variable/helti-c-12m-hp:MED_SUPP_VITD_C_12M:Dataschema" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
-    <hyperlink ref="A29" r:id="rId23" display="https://www.maelstrom-research.org/variable/canpath-f1-hrfq-hp:F1_WH_HRT_EVER:Dataschema" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
-    <hyperlink ref="A31" r:id="rId24" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_DIAB:Dataschema" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
-    <hyperlink ref="A33" r:id="rId25" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_HYP:Dataschema" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
-    <hyperlink ref="A35" r:id="rId26" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_CVD:Dataschema" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
-    <hyperlink ref="A37" r:id="rId27" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_CVD:Dataschema" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
-    <hyperlink ref="A62" r:id="rId28" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:MED_STAT:Dataschema" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
-    <hyperlink ref="A64" r:id="rId29" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:MED_NSAID:Dataschema" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
-    <hyperlink ref="A70" r:id="rId30" display="https://www.maelstrom-research.org/variable/canpath-f1-hrfq-hp:F1_DIS_MI_AGE:Dataschema" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
-    <hyperlink ref="A82" r:id="rId31" display="https://www.maelstrom-research.org/variable/canpath-f1-hrfq-hp:F1_DIS_DIAB_TYPE2:Dataschema" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
+    <hyperlink ref="A24" r:id="rId2" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:SMOKE_ST:Dataschema" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="A34" r:id="rId3" display="https://www.maelstrom-research.org/variable/canpath-f1-hrfq-hp:F1_WH_HRT_EVER:Dataschema" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="A75" r:id="rId4" display="https://www.maelstrom-research.org/variable/canpath-f1-hrfq-hp:F1_DIS_MI_AGE:Dataschema" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="A38" r:id="rId5" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_HYP:Dataschema" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="A40" r:id="rId6" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_CVD:Dataschema" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="A67" r:id="rId7" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:MED_STAT:Dataschema" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="A69" r:id="rId8" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:MED_NSAID:Dataschema" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="A36" r:id="rId9" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_DIAB:Dataschema" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="A42" r:id="rId10" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_CVD:Dataschema" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="A18" r:id="rId11" display="https://www.maelstrom-research.org/variable/chpt-qual-hp:WRK_EMPLOYMENT:Dataschema" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="A28" r:id="rId12" display="https://www.maelstrom-research.org/variable/helti-c-12m-hp:MED_SUPP_VITD_C_12M:Dataschema" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="A87" r:id="rId13" display="https://www.maelstrom-research.org/variable/canpath-f1-hrfq-hp:F1_DIS_DIAB_TYPE2:Dataschema" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="A15" r:id="rId14" display="https://www.maelstrom-research.org/variable/chpt-qual-hp:WRK_EMPLOYMENT:Dataschema" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="A14" r:id="rId15" display="https://www.maelstrom-research.org/variable/chpt-qual-hp:WRK_EMPLOYMENT:Dataschema" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="A19" r:id="rId16" display="https://www.maelstrom-research.org/variable/chpt-qual-hp:WRK_EMPLOYMENT:Dataschema" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="A20" r:id="rId17" display="https://www.maelstrom-research.org/variable/chpt-qual-hp:WRK_EMPLOYMENT:Dataschema" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
+    <hyperlink ref="A17" r:id="rId18" display="https://www.maelstrom-research.org/variable/chpt-qual-hp:WRK_EMPLOYMENT:Dataschema" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
+    <hyperlink ref="A16" r:id="rId19" display="https://www.maelstrom-research.org/variable/chpt-qual-hp:WRK_EMPLOYMENT:Dataschema" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
+    <hyperlink ref="A23" r:id="rId20" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:SMOKE_ST:Dataschema" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
+    <hyperlink ref="A25" r:id="rId21" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:SMOKE_ST:Dataschema" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
+    <hyperlink ref="A27" r:id="rId22" display="https://www.maelstrom-research.org/variable/helti-c-12m-hp:MED_SUPP_VITD_C_12M:Dataschema" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
+    <hyperlink ref="A33" r:id="rId23" display="https://www.maelstrom-research.org/variable/canpath-f1-hrfq-hp:F1_WH_HRT_EVER:Dataschema" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
+    <hyperlink ref="A35" r:id="rId24" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_DIAB:Dataschema" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
+    <hyperlink ref="A37" r:id="rId25" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_HYP:Dataschema" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
+    <hyperlink ref="A39" r:id="rId26" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_CVD:Dataschema" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
+    <hyperlink ref="A41" r:id="rId27" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:PREV_CVD:Dataschema" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
+    <hyperlink ref="A66" r:id="rId28" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:MED_STAT:Dataschema" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
+    <hyperlink ref="A68" r:id="rId29" display="https://mica.mdc-berlin.de/variable/microbiome-in-health-and-disease-and-in-ageing:MED_NSAID:Dataschema" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
+    <hyperlink ref="A74" r:id="rId30" display="https://www.maelstrom-research.org/variable/canpath-f1-hrfq-hp:F1_DIS_MI_AGE:Dataschema" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
+    <hyperlink ref="A86" r:id="rId31" display="https://www.maelstrom-research.org/variable/canpath-f1-hrfq-hp:F1_DIS_DIAB_TYPE2:Dataschema" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId32"/>
@@ -4089,6 +4145,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Zeit xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xsi:nil="true"/>
@@ -4098,15 +4163,6 @@
     <TaxCatchAll xmlns="12535b08-222e-45d2-b6db-15019f1afee6" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4129,6 +4185,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBBE8B2F-371B-4499-AB2D-BE5C88E1FE7D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EB6D834-F5F1-4875-9BFF-E74D4F6F598A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4137,12 +4201,4 @@
     <ds:schemaRef ds:uri="12535b08-222e-45d2-b6db-15019f1afee6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBBE8B2F-371B-4499-AB2D-BE5C88E1FE7D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/rmonize/data_schema/Dataschema_P2.xlsx
+++ b/rmonize/data_schema/Dataschema_P2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\rmonize\data_schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007AC5BF-B6C4-4BD2-A3C0-86BAE84EA577}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D1CC84-4021-42EB-8577-902CCDA5F1A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14895" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
@@ -70,9 +70,6 @@
     <t>EDU_LEVEL</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>EMPLOY</t>
   </si>
   <si>
@@ -812,6 +809,9 @@
   </si>
   <si>
     <t>Other</t>
+  </si>
+  <si>
+    <t>Highest level of education [ISCED 2011]</t>
   </si>
 </sst>
 </file>
@@ -1252,7 +1252,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
@@ -1263,10 +1263,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -1277,10 +1277,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
         <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
@@ -1291,10 +1291,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
         <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -1305,10 +1305,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
         <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -1319,10 +1319,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
         <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
@@ -1333,10 +1333,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
         <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -1347,10 +1347,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
         <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -1361,10 +1361,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
         <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>29</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -1375,10 +1375,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
         <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
@@ -1389,10 +1389,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
         <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
@@ -1403,10 +1403,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
         <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>35</v>
       </c>
       <c r="D16" t="s">
         <v>6</v>
@@ -1417,10 +1417,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
         <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>37</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
@@ -1431,10 +1431,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
         <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>39</v>
       </c>
       <c r="D18" t="s">
         <v>6</v>
@@ -1445,10 +1445,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
         <v>40</v>
-      </c>
-      <c r="C19" t="s">
-        <v>41</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -1459,10 +1459,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
         <v>42</v>
-      </c>
-      <c r="C20" t="s">
-        <v>43</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -1473,10 +1473,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
         <v>44</v>
-      </c>
-      <c r="C21" t="s">
-        <v>45</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -1487,10 +1487,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
         <v>46</v>
-      </c>
-      <c r="C22" t="s">
-        <v>47</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -1501,10 +1501,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
         <v>48</v>
-      </c>
-      <c r="C23" t="s">
-        <v>49</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1515,10 +1515,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
         <v>50</v>
-      </c>
-      <c r="C24" t="s">
-        <v>51</v>
       </c>
       <c r="D24" t="s">
         <v>6</v>
@@ -1529,10 +1529,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
         <v>52</v>
-      </c>
-      <c r="C25" t="s">
-        <v>53</v>
       </c>
       <c r="D25" t="s">
         <v>6</v>
@@ -1543,10 +1543,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
         <v>54</v>
-      </c>
-      <c r="C26" t="s">
-        <v>55</v>
       </c>
       <c r="D26" t="s">
         <v>6</v>
@@ -1557,10 +1557,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
         <v>56</v>
-      </c>
-      <c r="C27" t="s">
-        <v>57</v>
       </c>
       <c r="D27" t="s">
         <v>6</v>
@@ -1571,10 +1571,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" t="s">
         <v>58</v>
-      </c>
-      <c r="C28" t="s">
-        <v>59</v>
       </c>
       <c r="D28" t="s">
         <v>6</v>
@@ -1585,10 +1585,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
         <v>60</v>
-      </c>
-      <c r="C29" t="s">
-        <v>61</v>
       </c>
       <c r="D29" t="s">
         <v>6</v>
@@ -1599,10 +1599,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
         <v>62</v>
-      </c>
-      <c r="C30" t="s">
-        <v>63</v>
       </c>
       <c r="D30" t="s">
         <v>6</v>
@@ -1613,10 +1613,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
         <v>64</v>
-      </c>
-      <c r="C31" t="s">
-        <v>65</v>
       </c>
       <c r="D31" t="s">
         <v>6</v>
@@ -1627,10 +1627,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" t="s">
         <v>66</v>
-      </c>
-      <c r="C32" t="s">
-        <v>67</v>
       </c>
       <c r="D32" t="s">
         <v>6</v>
@@ -1641,10 +1641,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" t="s">
         <v>68</v>
-      </c>
-      <c r="C33" t="s">
-        <v>69</v>
       </c>
       <c r="D33" t="s">
         <v>6</v>
@@ -1655,10 +1655,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
         <v>70</v>
-      </c>
-      <c r="C34" t="s">
-        <v>71</v>
       </c>
       <c r="D34" t="s">
         <v>6</v>
@@ -1669,10 +1669,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
         <v>72</v>
-      </c>
-      <c r="C35" t="s">
-        <v>73</v>
       </c>
       <c r="D35" t="s">
         <v>6</v>
@@ -1683,10 +1683,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" t="s">
         <v>74</v>
-      </c>
-      <c r="C36" t="s">
-        <v>75</v>
       </c>
       <c r="D36" t="s">
         <v>6</v>
@@ -1697,10 +1697,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" t="s">
         <v>76</v>
-      </c>
-      <c r="C37" t="s">
-        <v>77</v>
       </c>
       <c r="D37" t="s">
         <v>6</v>
@@ -1711,10 +1711,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" t="s">
         <v>78</v>
-      </c>
-      <c r="C38" t="s">
-        <v>79</v>
       </c>
       <c r="D38" t="s">
         <v>6</v>
@@ -1725,10 +1725,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" t="s">
         <v>80</v>
-      </c>
-      <c r="C39" t="s">
-        <v>81</v>
       </c>
       <c r="D39" t="s">
         <v>6</v>
@@ -1739,10 +1739,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" t="s">
         <v>82</v>
-      </c>
-      <c r="C40" t="s">
-        <v>83</v>
       </c>
       <c r="D40" t="s">
         <v>6</v>
@@ -1753,10 +1753,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -1767,10 +1767,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" t="s">
         <v>85</v>
-      </c>
-      <c r="C42" t="s">
-        <v>86</v>
       </c>
       <c r="D42" t="s">
         <v>6</v>
@@ -1781,10 +1781,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -1795,10 +1795,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" t="s">
         <v>88</v>
-      </c>
-      <c r="C44" t="s">
-        <v>89</v>
       </c>
       <c r="D44" t="s">
         <v>6</v>
@@ -1809,10 +1809,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
@@ -1823,10 +1823,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" t="s">
         <v>91</v>
-      </c>
-      <c r="C46" t="s">
-        <v>92</v>
       </c>
       <c r="D46" t="s">
         <v>6</v>
@@ -1837,10 +1837,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C47" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
@@ -1851,10 +1851,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" t="s">
         <v>94</v>
-      </c>
-      <c r="C48" t="s">
-        <v>95</v>
       </c>
       <c r="D48" t="s">
         <v>6</v>
@@ -1865,10 +1865,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C49" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
@@ -1879,10 +1879,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" t="s">
         <v>97</v>
-      </c>
-      <c r="C50" t="s">
-        <v>98</v>
       </c>
       <c r="D50" t="s">
         <v>6</v>
@@ -1893,10 +1893,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C51" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -1907,10 +1907,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" t="s">
         <v>100</v>
-      </c>
-      <c r="C52" t="s">
-        <v>101</v>
       </c>
       <c r="D52" t="s">
         <v>6</v>
@@ -1921,10 +1921,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C53" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -1935,10 +1935,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" t="s">
         <v>103</v>
-      </c>
-      <c r="C54" t="s">
-        <v>104</v>
       </c>
       <c r="D54" t="s">
         <v>6</v>
@@ -1949,10 +1949,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C55" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -1963,10 +1963,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>105</v>
+      </c>
+      <c r="C56" t="s">
         <v>106</v>
-      </c>
-      <c r="C56" t="s">
-        <v>107</v>
       </c>
       <c r="D56" t="s">
         <v>6</v>
@@ -1977,10 +1977,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C57" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -1991,10 +1991,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>108</v>
+      </c>
+      <c r="C58" t="s">
         <v>109</v>
-      </c>
-      <c r="C58" t="s">
-        <v>110</v>
       </c>
       <c r="D58" t="s">
         <v>6</v>
@@ -2005,13 +2005,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>110</v>
+      </c>
+      <c r="C59" t="s">
         <v>111</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>112</v>
-      </c>
-      <c r="D59" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2019,10 +2019,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C60" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
@@ -2033,10 +2033,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>114</v>
+      </c>
+      <c r="C61" t="s">
         <v>115</v>
-      </c>
-      <c r="C61" t="s">
-        <v>116</v>
       </c>
       <c r="D61" t="s">
         <v>6</v>
@@ -2047,10 +2047,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C62" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
@@ -2061,10 +2061,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>117</v>
+      </c>
+      <c r="C63" t="s">
         <v>118</v>
-      </c>
-      <c r="C63" t="s">
-        <v>119</v>
       </c>
       <c r="D63" t="s">
         <v>6</v>
@@ -2075,10 +2075,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>119</v>
+      </c>
+      <c r="C64" t="s">
         <v>120</v>
-      </c>
-      <c r="C64" t="s">
-        <v>121</v>
       </c>
       <c r="D64" t="s">
         <v>6</v>
@@ -2089,10 +2089,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>121</v>
+      </c>
+      <c r="C65" t="s">
         <v>122</v>
-      </c>
-      <c r="C65" t="s">
-        <v>123</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
@@ -2103,10 +2103,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>123</v>
+      </c>
+      <c r="C66" t="s">
         <v>124</v>
-      </c>
-      <c r="C66" t="s">
-        <v>125</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
@@ -2117,10 +2117,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" t="s">
         <v>126</v>
-      </c>
-      <c r="C67" t="s">
-        <v>127</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
@@ -2131,10 +2131,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>127</v>
+      </c>
+      <c r="C68" t="s">
         <v>128</v>
-      </c>
-      <c r="C68" t="s">
-        <v>129</v>
       </c>
       <c r="D68" t="s">
         <v>11</v>
@@ -2145,10 +2145,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" t="s">
         <v>130</v>
-      </c>
-      <c r="C69" t="s">
-        <v>131</v>
       </c>
       <c r="D69" t="s">
         <v>11</v>
@@ -2159,10 +2159,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>131</v>
+      </c>
+      <c r="C70" t="s">
         <v>132</v>
-      </c>
-      <c r="C70" t="s">
-        <v>133</v>
       </c>
       <c r="D70" t="s">
         <v>11</v>
@@ -2173,10 +2173,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>133</v>
+      </c>
+      <c r="C71" t="s">
         <v>134</v>
-      </c>
-      <c r="C71" t="s">
-        <v>135</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -2187,10 +2187,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>135</v>
+      </c>
+      <c r="C72" t="s">
         <v>136</v>
-      </c>
-      <c r="C72" t="s">
-        <v>137</v>
       </c>
       <c r="D72" t="s">
         <v>11</v>
@@ -2201,10 +2201,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>137</v>
+      </c>
+      <c r="C73" t="s">
         <v>138</v>
-      </c>
-      <c r="C73" t="s">
-        <v>139</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
@@ -2215,10 +2215,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>139</v>
+      </c>
+      <c r="C74" t="s">
         <v>140</v>
-      </c>
-      <c r="C74" t="s">
-        <v>141</v>
       </c>
       <c r="D74" t="s">
         <v>11</v>
@@ -2229,10 +2229,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>141</v>
+      </c>
+      <c r="C75" t="s">
         <v>142</v>
-      </c>
-      <c r="C75" t="s">
-        <v>143</v>
       </c>
       <c r="D75" t="s">
         <v>11</v>
@@ -2243,10 +2243,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>143</v>
+      </c>
+      <c r="C76" t="s">
         <v>144</v>
-      </c>
-      <c r="C76" t="s">
-        <v>145</v>
       </c>
       <c r="D76" t="s">
         <v>11</v>
@@ -2257,10 +2257,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
+        <v>145</v>
+      </c>
+      <c r="C77" t="s">
         <v>146</v>
-      </c>
-      <c r="C77" t="s">
-        <v>147</v>
       </c>
       <c r="D77" t="s">
         <v>11</v>
@@ -2271,10 +2271,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>147</v>
+      </c>
+      <c r="C78" t="s">
         <v>148</v>
-      </c>
-      <c r="C78" t="s">
-        <v>149</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
@@ -2285,10 +2285,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>149</v>
+      </c>
+      <c r="C79" t="s">
         <v>150</v>
-      </c>
-      <c r="C79" t="s">
-        <v>151</v>
       </c>
       <c r="D79" t="s">
         <v>11</v>
@@ -2299,10 +2299,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>151</v>
+      </c>
+      <c r="C80" t="s">
         <v>152</v>
-      </c>
-      <c r="C80" t="s">
-        <v>153</v>
       </c>
       <c r="D80" t="s">
         <v>11</v>
@@ -2313,10 +2313,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>153</v>
+      </c>
+      <c r="C81" t="s">
         <v>154</v>
-      </c>
-      <c r="C81" t="s">
-        <v>155</v>
       </c>
       <c r="D81" t="s">
         <v>11</v>
@@ -2327,10 +2327,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>155</v>
+      </c>
+      <c r="C82" t="s">
         <v>156</v>
-      </c>
-      <c r="C82" t="s">
-        <v>157</v>
       </c>
       <c r="D82" t="s">
         <v>11</v>
@@ -2341,10 +2341,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>157</v>
+      </c>
+      <c r="C83" t="s">
         <v>158</v>
-      </c>
-      <c r="C83" t="s">
-        <v>159</v>
       </c>
       <c r="D83" t="s">
         <v>11</v>
@@ -2355,10 +2355,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>159</v>
+      </c>
+      <c r="C84" t="s">
         <v>160</v>
-      </c>
-      <c r="C84" t="s">
-        <v>161</v>
       </c>
       <c r="D84" t="s">
         <v>11</v>
@@ -2369,10 +2369,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>161</v>
+      </c>
+      <c r="C85" t="s">
         <v>162</v>
-      </c>
-      <c r="C85" t="s">
-        <v>163</v>
       </c>
       <c r="D85" t="s">
         <v>11</v>
@@ -2383,10 +2383,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>163</v>
+      </c>
+      <c r="C86" t="s">
         <v>164</v>
-      </c>
-      <c r="C86" t="s">
-        <v>165</v>
       </c>
       <c r="D86" t="s">
         <v>11</v>
@@ -2397,10 +2397,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>165</v>
+      </c>
+      <c r="C87" t="s">
         <v>166</v>
-      </c>
-      <c r="C87" t="s">
-        <v>167</v>
       </c>
       <c r="D87" t="s">
         <v>11</v>
@@ -2411,10 +2411,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>167</v>
+      </c>
+      <c r="C88" t="s">
         <v>168</v>
-      </c>
-      <c r="C88" t="s">
-        <v>169</v>
       </c>
       <c r="D88" t="s">
         <v>11</v>
@@ -2425,10 +2425,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>169</v>
+      </c>
+      <c r="C89" t="s">
         <v>170</v>
-      </c>
-      <c r="C89" t="s">
-        <v>171</v>
       </c>
       <c r="D89" t="s">
         <v>11</v>
@@ -2439,10 +2439,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>171</v>
+      </c>
+      <c r="C90" t="s">
         <v>172</v>
-      </c>
-      <c r="C90" t="s">
-        <v>173</v>
       </c>
       <c r="D90" t="s">
         <v>11</v>
@@ -2453,10 +2453,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>173</v>
+      </c>
+      <c r="C91" t="s">
         <v>174</v>
-      </c>
-      <c r="C91" t="s">
-        <v>175</v>
       </c>
       <c r="D91" t="s">
         <v>11</v>
@@ -2467,10 +2467,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
+        <v>175</v>
+      </c>
+      <c r="C92" t="s">
         <v>176</v>
-      </c>
-      <c r="C92" t="s">
-        <v>177</v>
       </c>
       <c r="D92" t="s">
         <v>11</v>
@@ -2481,10 +2481,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>177</v>
+      </c>
+      <c r="C93" t="s">
         <v>178</v>
-      </c>
-      <c r="C93" t="s">
-        <v>179</v>
       </c>
       <c r="D93" t="s">
         <v>11</v>
@@ -2495,10 +2495,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
+        <v>179</v>
+      </c>
+      <c r="C94" t="s">
         <v>180</v>
-      </c>
-      <c r="C94" t="s">
-        <v>181</v>
       </c>
       <c r="D94" t="s">
         <v>11</v>
@@ -2509,10 +2509,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C95" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D95" t="s">
         <v>11</v>
@@ -2523,10 +2523,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C96" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D96" t="s">
         <v>11</v>
@@ -2537,10 +2537,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>183</v>
+      </c>
+      <c r="C97" t="s">
         <v>184</v>
-      </c>
-      <c r="C97" t="s">
-        <v>185</v>
       </c>
       <c r="D97" t="s">
         <v>11</v>
@@ -2551,10 +2551,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>185</v>
+      </c>
+      <c r="C98" t="s">
         <v>186</v>
-      </c>
-      <c r="C98" t="s">
-        <v>187</v>
       </c>
       <c r="D98" t="s">
         <v>11</v>
@@ -2565,10 +2565,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>187</v>
+      </c>
+      <c r="C99" t="s">
         <v>188</v>
-      </c>
-      <c r="C99" t="s">
-        <v>189</v>
       </c>
       <c r="D99" t="s">
         <v>11</v>
@@ -2579,10 +2579,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>189</v>
+      </c>
+      <c r="C100" t="s">
         <v>190</v>
-      </c>
-      <c r="C100" t="s">
-        <v>191</v>
       </c>
       <c r="D100" t="s">
         <v>11</v>
@@ -2593,10 +2593,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>191</v>
+      </c>
+      <c r="C101" t="s">
         <v>192</v>
-      </c>
-      <c r="C101" t="s">
-        <v>193</v>
       </c>
       <c r="D101" t="s">
         <v>11</v>
@@ -2607,10 +2607,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
+        <v>193</v>
+      </c>
+      <c r="C102" t="s">
         <v>194</v>
-      </c>
-      <c r="C102" t="s">
-        <v>195</v>
       </c>
       <c r="D102" t="s">
         <v>11</v>
@@ -2621,10 +2621,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>195</v>
+      </c>
+      <c r="C103" t="s">
         <v>196</v>
-      </c>
-      <c r="C103" t="s">
-        <v>197</v>
       </c>
       <c r="D103" t="s">
         <v>11</v>
@@ -2635,10 +2635,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
+        <v>197</v>
+      </c>
+      <c r="C104" t="s">
         <v>198</v>
-      </c>
-      <c r="C104" t="s">
-        <v>199</v>
       </c>
       <c r="D104" t="s">
         <v>11</v>
@@ -2649,10 +2649,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>199</v>
+      </c>
+      <c r="C105" t="s">
         <v>200</v>
-      </c>
-      <c r="C105" t="s">
-        <v>201</v>
       </c>
       <c r="D105" t="s">
         <v>11</v>
@@ -2663,10 +2663,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>201</v>
+      </c>
+      <c r="C106" t="s">
         <v>202</v>
-      </c>
-      <c r="C106" t="s">
-        <v>203</v>
       </c>
       <c r="D106" t="s">
         <v>11</v>
@@ -2677,10 +2677,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
+        <v>203</v>
+      </c>
+      <c r="C107" t="s">
         <v>204</v>
-      </c>
-      <c r="C107" t="s">
-        <v>205</v>
       </c>
       <c r="D107" t="s">
         <v>11</v>
@@ -2691,10 +2691,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
+        <v>205</v>
+      </c>
+      <c r="C108" t="s">
         <v>206</v>
-      </c>
-      <c r="C108" t="s">
-        <v>207</v>
       </c>
       <c r="D108" t="s">
         <v>11</v>
@@ -2705,10 +2705,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
+        <v>207</v>
+      </c>
+      <c r="C109" t="s">
         <v>208</v>
-      </c>
-      <c r="C109" t="s">
-        <v>209</v>
       </c>
       <c r="D109" t="s">
         <v>6</v>
@@ -2738,7 +2738,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -2752,7 +2752,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2763,7 +2763,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -2774,7 +2774,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2785,7 +2785,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2796,7 +2796,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -2807,7 +2807,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -2818,7 +2818,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2829,7 +2829,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -2840,7 +2840,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -2851,7 +2851,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -2862,7 +2862,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C12">
         <v>8</v>
@@ -2873,7 +2873,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C13">
         <v>9</v>
@@ -2881,10 +2881,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -2903,10 +2903,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C17">
         <v>4</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C20">
         <v>7</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2969,10 +2969,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -2980,10 +2980,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -3002,10 +3002,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C26">
         <v>4</v>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -3035,10 +3035,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3057,10 +3057,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C32">
         <v>3</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -3101,10 +3101,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -3112,10 +3112,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B36" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -3134,10 +3134,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -3145,10 +3145,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -3156,10 +3156,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -3167,10 +3167,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B40" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -3178,10 +3178,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B42" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B43" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B46" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B48" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -3277,10 +3277,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B50" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -3288,10 +3288,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B52" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B53" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -3343,10 +3343,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B56" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B58" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -3387,10 +3387,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B60" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -3398,10 +3398,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -3409,10 +3409,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B62" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -3420,10 +3420,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B64" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B66" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B67" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B68" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -3486,10 +3486,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B69" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B70" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B71" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -3519,10 +3519,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B72" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B73" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B75" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3574,10 +3574,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -3585,10 +3585,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B78" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="80" spans="1:3" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B80" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -3618,10 +3618,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B81" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -3629,10 +3629,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B82" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B83" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B84" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -3662,10 +3662,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B85" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B86" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -3684,10 +3684,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B87" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -3695,10 +3695,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B88" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -3706,10 +3706,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B89" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -3717,10 +3717,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B90" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -3728,10 +3728,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B91" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -3739,10 +3739,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B92" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -3750,10 +3750,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B93" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B94" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B95" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -3783,10 +3783,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B96" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B97" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -3805,10 +3805,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B98" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C98">
         <v>2</v>
@@ -3816,10 +3816,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B99" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C99">
         <v>3</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B100" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C100">
         <v>4</v>
@@ -3838,10 +3838,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B101" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C101">
         <v>5</v>
@@ -3849,10 +3849,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B102" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C102">
         <v>6</v>
@@ -4145,15 +4145,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Zeit xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xsi:nil="true"/>
@@ -4163,6 +4154,15 @@
     <TaxCatchAll xmlns="12535b08-222e-45d2-b6db-15019f1afee6" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4185,14 +4185,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBBE8B2F-371B-4499-AB2D-BE5C88E1FE7D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EB6D834-F5F1-4875-9BFF-E74D4F6F598A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4201,4 +4193,12 @@
     <ds:schemaRef ds:uri="12535b08-222e-45d2-b6db-15019f1afee6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBBE8B2F-371B-4499-AB2D-BE5C88E1FE7D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>